--- a/artfynd/A 21670-2024 artfynd.xlsx
+++ b/artfynd/A 21670-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118676142</v>
+        <v>118676140</v>
       </c>
       <c r="B2" t="n">
-        <v>100124</v>
+        <v>79073</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1853</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>374979</v>
+        <v>374986</v>
       </c>
       <c r="R2" t="n">
-        <v>6871538</v>
+        <v>6871399</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676140</v>
+        <v>118676145</v>
       </c>
       <c r="B3" t="n">
-        <v>79073</v>
+        <v>77868</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>374986</v>
+        <v>374864</v>
       </c>
       <c r="R3" t="n">
-        <v>6871399</v>
+        <v>6871388</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118676145</v>
+        <v>118676142</v>
       </c>
       <c r="B4" t="n">
-        <v>77868</v>
+        <v>100124</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>1853</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>374864</v>
+        <v>374979</v>
       </c>
       <c r="R4" t="n">
-        <v>6871388</v>
+        <v>6871538</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 21670-2024 artfynd.xlsx
+++ b/artfynd/A 21670-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676145</v>
+        <v>118676141</v>
       </c>
       <c r="B3" t="n">
-        <v>77868</v>
+        <v>78221</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>374864</v>
+        <v>374986</v>
       </c>
       <c r="R3" t="n">
-        <v>6871388</v>
+        <v>6871399</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118676142</v>
+        <v>118676145</v>
       </c>
       <c r="B4" t="n">
-        <v>100124</v>
+        <v>77868</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1853</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>374979</v>
+        <v>374864</v>
       </c>
       <c r="R4" t="n">
-        <v>6871538</v>
+        <v>6871388</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118676141</v>
+        <v>118676142</v>
       </c>
       <c r="B6" t="n">
-        <v>78221</v>
+        <v>100124</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>1853</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>374986</v>
+        <v>374979</v>
       </c>
       <c r="R6" t="n">
-        <v>6871399</v>
+        <v>6871538</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 21670-2024 artfynd.xlsx
+++ b/artfynd/A 21670-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118676140</v>
+        <v>118676142</v>
       </c>
       <c r="B2" t="n">
-        <v>79073</v>
+        <v>100131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>1853</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>374986</v>
+        <v>374979</v>
       </c>
       <c r="R2" t="n">
-        <v>6871399</v>
+        <v>6871538</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676141</v>
+        <v>118676143</v>
       </c>
       <c r="B3" t="n">
-        <v>78221</v>
+        <v>78227</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>374986</v>
+        <v>375048</v>
       </c>
       <c r="R3" t="n">
-        <v>6871399</v>
+        <v>6871517</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +900,7 @@
         <v>118676145</v>
       </c>
       <c r="B4" t="n">
-        <v>77868</v>
+        <v>77875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118676143</v>
+        <v>118676140</v>
       </c>
       <c r="B5" t="n">
-        <v>78220</v>
+        <v>79080</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>375048</v>
+        <v>374986</v>
       </c>
       <c r="R5" t="n">
-        <v>6871517</v>
+        <v>6871399</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118676142</v>
+        <v>118676141</v>
       </c>
       <c r="B6" t="n">
-        <v>100124</v>
+        <v>78228</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1853</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>374979</v>
+        <v>374986</v>
       </c>
       <c r="R6" t="n">
-        <v>6871538</v>
+        <v>6871399</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 21670-2024 artfynd.xlsx
+++ b/artfynd/A 21670-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118676142</v>
+        <v>118676145</v>
       </c>
       <c r="B2" t="n">
-        <v>100131</v>
+        <v>77875</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1853</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>374979</v>
+        <v>374864</v>
       </c>
       <c r="R2" t="n">
-        <v>6871538</v>
+        <v>6871388</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676143</v>
+        <v>118676142</v>
       </c>
       <c r="B3" t="n">
-        <v>78227</v>
+        <v>100131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>1853</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>375048</v>
+        <v>374979</v>
       </c>
       <c r="R3" t="n">
-        <v>6871517</v>
+        <v>6871538</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118676145</v>
+        <v>118676140</v>
       </c>
       <c r="B4" t="n">
-        <v>77875</v>
+        <v>79080</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>374864</v>
+        <v>374986</v>
       </c>
       <c r="R4" t="n">
-        <v>6871388</v>
+        <v>6871399</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118676140</v>
+        <v>118676141</v>
       </c>
       <c r="B5" t="n">
-        <v>79080</v>
+        <v>78228</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118676141</v>
+        <v>118676143</v>
       </c>
       <c r="B6" t="n">
-        <v>78228</v>
+        <v>78227</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>374986</v>
+        <v>375048</v>
       </c>
       <c r="R6" t="n">
-        <v>6871399</v>
+        <v>6871517</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
